--- a/data/trans_dic/P12_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,08</t>
+          <t>2,96; 7,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,26</t>
+          <t>3,38; 8,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,89</t>
+          <t>3,12; 7,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,72</t>
+          <t>6,21; 11,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,23</t>
+          <t>3,93; 9,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 11,31</t>
+          <t>4,25; 11,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,54</t>
+          <t>2,09; 6,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,9</t>
+          <t>6,56; 10,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,16</t>
+          <t>3,69; 6,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,45</t>
+          <t>4,17; 8,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,18</t>
+          <t>3,16; 6,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,61</t>
+          <t>6,92; 10,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,53</t>
+          <t>1,91; 6,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,33</t>
+          <t>3,95; 9,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,57</t>
+          <t>4,4; 9,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,85</t>
+          <t>6,84; 12,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,13</t>
+          <t>5,74; 11,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 14,19</t>
+          <t>6,79; 13,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 12,37</t>
+          <t>6,23; 12,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,59</t>
+          <t>6,86; 12,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,98</t>
+          <t>4,31; 7,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,11</t>
+          <t>5,8; 10,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,81</t>
+          <t>5,88; 9,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,31</t>
+          <t>7,46; 11,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,3</t>
+          <t>3,4; 7,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 11,42</t>
+          <t>6,99; 11,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,79</t>
+          <t>6,03; 10,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,38</t>
+          <t>2,86; 13,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,34</t>
+          <t>7,41; 17,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 15,64</t>
+          <t>7,9; 15,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 20,08</t>
+          <t>8,64; 20,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,35; 19,67</t>
+          <t>10,61; 19,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,85</t>
+          <t>5,0; 8,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,79</t>
+          <t>7,81; 11,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,9</t>
+          <t>7,45; 12,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 14,06</t>
+          <t>3,43; 13,69</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,44</t>
+          <t>4,87; 7,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 11,85</t>
+          <t>8,22; 11,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,98</t>
+          <t>6,66; 9,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 15,37</t>
+          <t>10,16; 15,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,05</t>
+          <t>6,11; 10,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 15,99</t>
+          <t>10,36; 15,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,17</t>
+          <t>7,87; 12,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,91</t>
+          <t>5,16; 13,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,96</t>
+          <t>5,76; 7,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 12,74</t>
+          <t>9,63; 12,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,33</t>
+          <t>7,6; 10,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 13,57</t>
+          <t>7,72; 13,41</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,95</t>
+          <t>3,07; 7,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,98</t>
+          <t>6,0; 11,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,11</t>
+          <t>7,32; 12,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,42; 13,9</t>
+          <t>8,29; 13,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,91</t>
+          <t>6,64; 11,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 21,13</t>
+          <t>15,41; 21,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,83; 21,81</t>
+          <t>15,73; 21,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,23; 19,47</t>
+          <t>12,45; 19,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,3</t>
+          <t>5,76; 9,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,35</t>
+          <t>12,35; 16,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 16,6</t>
+          <t>12,7; 16,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,32</t>
+          <t>11,77; 16,59</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,01</t>
+          <t>1,88; 6,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,77</t>
+          <t>3,11; 8,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,88</t>
+          <t>1,07; 4,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 11,11</t>
+          <t>3,06; 12,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,55</t>
+          <t>7,35; 10,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,46; 15,59</t>
+          <t>11,65; 15,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,12</t>
+          <t>9,66; 14,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 18,76</t>
+          <t>14,25; 18,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,29</t>
+          <t>6,56; 9,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,12; 13,65</t>
+          <t>10,11; 13,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 11,79</t>
+          <t>8,42; 11,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,93; 16,08</t>
+          <t>11,95; 15,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 5,93</t>
+          <t>4,32; 5,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,13</t>
+          <t>7,18; 9,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,4</t>
+          <t>6,45; 8,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 11,18</t>
+          <t>7,57; 11,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 9,58</t>
+          <t>7,57; 9,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,12; 14,52</t>
+          <t>12,05; 14,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,98</t>
+          <t>10,69; 12,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,61; 14,26</t>
+          <t>10,67; 14,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,49</t>
+          <t>6,25; 7,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,95; 11,45</t>
+          <t>10,0; 11,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,97; 10,39</t>
+          <t>8,93; 10,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 12,51</t>
+          <t>9,75; 12,38</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14365; 33553</t>
+          <t>14037; 33405</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15269; 36116</t>
+          <t>14794; 35664</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13551; 33860</t>
+          <t>13381; 32072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32167; 59201</t>
+          <t>31382; 58639</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11823; 28300</t>
+          <t>12067; 28032</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13924; 35436</t>
+          <t>13325; 34910</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7813; 22686</t>
+          <t>7262; 22899</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29372; 48787</t>
+          <t>29360; 48365</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28615; 55861</t>
+          <t>28825; 54169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33568; 63414</t>
+          <t>31337; 60557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23975; 47950</t>
+          <t>24556; 49767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66760; 101112</t>
+          <t>65909; 99380</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7001; 23959</t>
+          <t>6993; 23446</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16104; 39064</t>
+          <t>16537; 39312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16018; 35980</t>
+          <t>16553; 35387</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30318; 58100</t>
+          <t>30949; 57061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20143; 41403</t>
+          <t>21332; 43344</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22521; 47957</t>
+          <t>22948; 47081</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22717; 45907</t>
+          <t>23143; 46790</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26812; 48176</t>
+          <t>26254; 46826</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31684; 58948</t>
+          <t>31862; 58318</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45574; 76528</t>
+          <t>43888; 78179</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43543; 73310</t>
+          <t>43933; 73947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62819; 94402</t>
+          <t>62292; 95073</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18071; 39575</t>
+          <t>18447; 38907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43728; 71587</t>
+          <t>43819; 72638</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30432; 56094</t>
+          <t>31332; 55876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18881; 89340</t>
+          <t>19078; 90346</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12810; 29090</t>
+          <t>12428; 29520</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20063; 40678</t>
+          <t>20563; 41266</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14179; 33364</t>
+          <t>14358; 34609</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18942; 32839</t>
+          <t>17717; 32374</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35252; 62883</t>
+          <t>35476; 62534</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68909; 104568</t>
+          <t>69254; 105047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49735; 81641</t>
+          <t>51072; 83113</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31451; 117356</t>
+          <t>28671; 114256</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60547; 92183</t>
+          <t>60274; 92639</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94391; 137145</t>
+          <t>95058; 134682</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75943; 114509</t>
+          <t>76457; 113699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103396; 158892</t>
+          <t>105035; 156616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43177; 71754</t>
+          <t>43612; 72728</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80708; 122241</t>
+          <t>79177; 118817</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64885; 100430</t>
+          <t>64898; 100234</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53025; 135917</t>
+          <t>50387; 134179</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>110131; 155414</t>
+          <t>112425; 153872</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>186587; 244877</t>
+          <t>185043; 243280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>152977; 203728</t>
+          <t>150009; 202346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>157229; 272881</t>
+          <t>155286; 269592</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10789; 27862</t>
+          <t>10760; 27988</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31061; 56073</t>
+          <t>30640; 56703</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46956; 75181</t>
+          <t>45423; 75754</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39863; 65788</t>
+          <t>39244; 64673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38876; 67710</t>
+          <t>37775; 65140</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>117501; 160506</t>
+          <t>117047; 161706</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>116880; 161006</t>
+          <t>116155; 159599</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102753; 163650</t>
+          <t>104636; 163964</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52814; 85501</t>
+          <t>52954; 84567</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155571; 207675</t>
+          <t>156907; 208433</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>170598; 225619</t>
+          <t>172544; 224733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>154434; 214449</t>
+          <t>154575; 217907</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5534; 17930</t>
+          <t>5601; 18530</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7949; 23311</t>
+          <t>8264; 22969</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2987; 14013</t>
+          <t>3086; 14209</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7053; 26721</t>
+          <t>7349; 29371</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92019; 131800</t>
+          <t>91807; 132482</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>127039; 172809</t>
+          <t>129126; 176243</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>105555; 152009</t>
+          <t>104011; 150792</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>108819; 142488</t>
+          <t>108265; 144202</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101607; 143682</t>
+          <t>101500; 143362</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>139071; 187590</t>
+          <t>138925; 187499</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113344; 160828</t>
+          <t>114881; 160200</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>119315; 160856</t>
+          <t>119558; 159166</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>142541; 194035</t>
+          <t>141301; 194280</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>243268; 311898</t>
+          <t>245435; 310526</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>219484; 284020</t>
+          <t>218107; 283660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>256172; 377230</t>
+          <t>255447; 379979</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>257302; 323540</t>
+          <t>255651; 320922</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>429636; 514708</t>
+          <t>426905; 511528</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>375604; 457417</t>
+          <t>376790; 456527</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>379322; 509862</t>
+          <t>381317; 513225</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>414893; 497835</t>
+          <t>415747; 494676</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>692315; 796836</t>
+          <t>695982; 805924</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>619606; 717477</t>
+          <t>616477; 714931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>686458; 868796</t>
+          <t>677060; 859993</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,05</t>
+          <t>2,82; 6,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,16</t>
+          <t>3,17; 8,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,47</t>
+          <t>3,25; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,61</t>
+          <t>6,15; 11,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,14</t>
+          <t>3,43; 8,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,14</t>
+          <t>4,19; 10,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,6</t>
+          <t>2,21; 6,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,81</t>
+          <t>7,09; 11,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,94</t>
+          <t>3,69; 6,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,07</t>
+          <t>4,35; 8,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,41</t>
+          <t>3,24; 6,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,43</t>
+          <t>7,14; 10,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,39</t>
+          <t>1,87; 6,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,39</t>
+          <t>4,0; 9,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,41</t>
+          <t>4,37; 9,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,62</t>
+          <t>7,21; 13,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 11,66</t>
+          <t>5,61; 11,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 13,93</t>
+          <t>6,71; 13,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 12,6</t>
+          <t>6,14; 12,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,24</t>
+          <t>7,4; 12,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,89</t>
+          <t>4,31; 7,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,33</t>
+          <t>5,75; 10,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 9,89</t>
+          <t>5,95; 9,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,39</t>
+          <t>7,83; 11,46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,17</t>
+          <t>3,38; 7,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,59</t>
+          <t>6,83; 11,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,75</t>
+          <t>6,01; 11,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 13,53</t>
+          <t>10,04; 16,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 17,59</t>
+          <t>7,31; 17,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 15,86</t>
+          <t>7,54; 15,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 20,83</t>
+          <t>8,35; 20,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 19,4</t>
+          <t>11,27; 20,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,81</t>
+          <t>4,95; 8,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,84</t>
+          <t>7,88; 11,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,12</t>
+          <t>7,16; 12,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 13,69</t>
+          <t>11,1; 16,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,48</t>
+          <t>4,88; 7,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,64</t>
+          <t>8,3; 12,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 9,91</t>
+          <t>6,69; 9,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 15,15</t>
+          <t>10,13; 13,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,18</t>
+          <t>6,01; 9,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,54</t>
+          <t>10,72; 15,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,15</t>
+          <t>7,97; 12,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,73</t>
+          <t>11,77; 15,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 7,88</t>
+          <t>5,67; 7,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 12,66</t>
+          <t>9,66; 12,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,26</t>
+          <t>7,62; 10,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,41</t>
+          <t>11,32; 14,21</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,98</t>
+          <t>2,89; 7,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,11</t>
+          <t>6,03; 10,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 12,2</t>
+          <t>7,64; 12,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,66</t>
+          <t>7,97; 13,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,45</t>
+          <t>6,8; 11,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,41; 21,29</t>
+          <t>15,37; 21,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 21,62</t>
+          <t>15,53; 21,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 19,51</t>
+          <t>17,04; 21,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,2</t>
+          <t>5,73; 9,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,35; 16,41</t>
+          <t>12,18; 16,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,7; 16,54</t>
+          <t>12,74; 16,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 16,59</t>
+          <t>13,97; 17,78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,21</t>
+          <t>1,86; 6,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,64</t>
+          <t>3,01; 8,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,95</t>
+          <t>1,09; 4,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 12,21</t>
+          <t>3,58; 12,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,61</t>
+          <t>7,42; 10,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,65; 15,9</t>
+          <t>11,45; 15,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,0</t>
+          <t>9,66; 13,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,25; 18,98</t>
+          <t>14,22; 18,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,27</t>
+          <t>6,66; 9,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,64</t>
+          <t>10,13; 13,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,42; 11,74</t>
+          <t>8,28; 11,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,95; 15,91</t>
+          <t>12,42; 16,47</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,94</t>
+          <t>4,38; 5,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,09</t>
+          <t>7,15; 9,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,39</t>
+          <t>6,55; 8,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,27</t>
+          <t>9,54; 11,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 9,5</t>
+          <t>7,6; 9,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,05; 14,43</t>
+          <t>12,07; 14,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,95</t>
+          <t>10,66; 12,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 14,36</t>
+          <t>13,66; 15,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 7,44</t>
+          <t>6,21; 7,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,0; 11,58</t>
+          <t>9,94; 11,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 10,35</t>
+          <t>8,89; 10,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,75; 12,38</t>
+          <t>11,91; 13,42</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43309</t>
+          <t>46195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>44473</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>90668</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14037; 33405</t>
+          <t>13355; 32744</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14794; 35664</t>
+          <t>13841; 35309</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13381; 32072</t>
+          <t>13929; 34052</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31382; 58639</t>
+          <t>33853; 64357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12067; 28032</t>
+          <t>10533; 27520</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13325; 34910</t>
+          <t>13126; 34108</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7262; 22899</t>
+          <t>7660; 22737</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29360; 48365</t>
+          <t>34619; 55807</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28825; 54169</t>
+          <t>28779; 54453</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31337; 60557</t>
+          <t>32679; 61031</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24556; 49767</t>
+          <t>25136; 49579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65909; 99380</t>
+          <t>74145; 109038</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>46536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>40688</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77508</t>
+          <t>87224</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6993; 23446</t>
+          <t>6863; 24081</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16537; 39312</t>
+          <t>16771; 39045</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16553; 35387</t>
+          <t>16441; 34963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30949; 57061</t>
+          <t>34824; 63223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21332; 43344</t>
+          <t>20856; 42845</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22948; 47081</t>
+          <t>22682; 46800</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23143; 46790</t>
+          <t>22784; 45158</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26254; 46826</t>
+          <t>31310; 52433</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31862; 58318</t>
+          <t>31841; 57957</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43888; 78179</t>
+          <t>43514; 76521</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43933; 73947</t>
+          <t>44452; 74236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62292; 95073</t>
+          <t>70933; 103904</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53362</t>
+          <t>60222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>28161</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78180</t>
+          <t>88384</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18447; 38907</t>
+          <t>18327; 38322</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43819; 72638</t>
+          <t>42815; 72270</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31332; 55876</t>
+          <t>31216; 57171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19078; 90346</t>
+          <t>47324; 76741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12428; 29520</t>
+          <t>12270; 30083</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20563; 41266</t>
+          <t>19616; 41128</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14358; 34609</t>
+          <t>13877; 33296</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17717; 32374</t>
+          <t>21123; 37632</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35476; 62534</t>
+          <t>35139; 60987</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69254; 105047</t>
+          <t>69890; 104396</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51072; 83113</t>
+          <t>49138; 82665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28671; 114256</t>
+          <t>73124; 106163</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127060</t>
+          <t>134788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>101210</t>
+          <t>117391</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>228270</t>
+          <t>252179</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60274; 92639</t>
+          <t>60440; 93873</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95058; 134682</t>
+          <t>96078; 138803</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76457; 113699</t>
+          <t>76819; 113998</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105035; 156616</t>
+          <t>114456; 157900</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43612; 72728</t>
+          <t>42909; 71382</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79177; 118817</t>
+          <t>81990; 121601</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64898; 100234</t>
+          <t>65780; 100053</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50387; 134179</t>
+          <t>101237; 134749</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112425; 153872</t>
+          <t>110622; 153624</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>185043; 243280</t>
+          <t>185669; 242094</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>150009; 202346</t>
+          <t>150358; 201647</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>155286; 269592</t>
+          <t>225352; 282903</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50663</t>
+          <t>58918</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>139625</t>
+          <t>158985</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>190289</t>
+          <t>217903</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10760; 27988</t>
+          <t>10125; 27167</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30640; 56703</t>
+          <t>30793; 55942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45423; 75754</t>
+          <t>47450; 75554</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39244; 64673</t>
+          <t>45105; 74477</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37775; 65140</t>
+          <t>38680; 65771</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>117047; 161706</t>
+          <t>116726; 161401</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>116155; 159599</t>
+          <t>114630; 158322</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>104636; 163964</t>
+          <t>141390; 180495</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52954; 84567</t>
+          <t>52713; 87238</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156907; 208433</t>
+          <t>154765; 205964</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>172544; 224733</t>
+          <t>173113; 227002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>154575; 217907</t>
+          <t>195046; 248169</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>124365</t>
+          <t>138480</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>138039</t>
+          <t>154841</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5601; 18530</t>
+          <t>5554; 18594</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8264; 22969</t>
+          <t>8003; 22995</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3086; 14209</t>
+          <t>3120; 13852</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7349; 29371</t>
+          <t>8483; 29815</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91807; 132482</t>
+          <t>92647; 130640</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>129126; 176243</t>
+          <t>126919; 171467</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>104011; 150792</t>
+          <t>104051; 148118</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>108265; 144202</t>
+          <t>119826; 158128</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101500; 143362</t>
+          <t>102996; 143667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>138925; 187499</t>
+          <t>139198; 189908</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114881; 160200</t>
+          <t>112909; 161728</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>119558; 159166</t>
+          <t>134118; 177852</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>330646</t>
+          <t>363020</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>463423</t>
+          <t>528178</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>794069</t>
+          <t>891198</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>141301; 194280</t>
+          <t>143318; 194785</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>245435; 310526</t>
+          <t>244327; 310965</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>218107; 283660</t>
+          <t>221385; 282867</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255447; 379979</t>
+          <t>327995; 406216</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>255651; 320922</t>
+          <t>256881; 321304</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>426905; 511528</t>
+          <t>427666; 512205</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>376790; 456527</t>
+          <t>375779; 457244</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>381317; 513225</t>
+          <t>495938; 567370</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>415747; 494676</t>
+          <t>412792; 497746</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>695982; 805924</t>
+          <t>691703; 800939</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>616477; 714931</t>
+          <t>614145; 717683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>677060; 859993</t>
+          <t>841765; 949065</t>
         </is>
       </c>
     </row>
